--- a/web/public/forms/nomubi-gubun-haeui.xlsx
+++ b/web/public/forms/nomubi-gubun-haeui.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="합의서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'합의서'!$A$1:$G$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'합의서'!$A$1:$G$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$G$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;;[Red]-#,##0&quot;원&quot;;&quot;&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%;&quot;&quot;"/>
+    <numFmt numFmtId="166" formatCode="&quot;(하도급액의 &quot;0.0%&quot;)&quot;;;&quot;&quot;"/>
+    <numFmt numFmtId="167" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,31 +38,78 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <sz val="11"/>
+      <color rgb="000F203F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="006B7280"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <sz val="16"/>
+      <color rgb="00111827"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <sz val="12"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -64,155 +119,82 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <bottom style="thin">
-        <color rgb="00000000"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -578,440 +560,1027 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
           <t>【서식2】  하도급계약 체결시</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>「노무비 구분관리 및 지급확인제」 세부사항 합의서</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>공 사 명</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="6" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>공  사  명</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>수급인</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>상호 및 대표자</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>영업소 소재지</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>하수급인</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>상호 및 대표자</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>하도급 공종</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>업종 및 등록번호</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>영업소 소재지
 (전화번호)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>하도급
 내용</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>공종</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>공  종</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>하도급내용</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도 급 액 : 
-하도급액 : 
-하도급율 : </t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>도 급 액</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>하도급액</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>하도급율</t>
+        </is>
+      </c>
+      <c r="E15" s="9">
+        <f>IF(OR(N(E13)=0,N(E14)=0),"",E14/E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>하도급계약상의
 직접노무비 또는
 노무비</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-    </row>
-    <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="10">
+        <f>IF(OR(N(D16)=0,N(E14)=0),"",D16/E14)</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="11">
+        <f>IF(AND(N(D16)&gt;0,N(E14)&gt;0,D16&gt;E14),"⚠ 노무비가 하도급액보다 큽니다 — 숫자를 확인하세요.",IF(AND(N(E14)&gt;0,N(E13)&gt;0,E14&gt;E13),"⚠ 하도급액이 도급액보다 큽니다 — 숫자를 확인하세요.",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="2" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>위 시설공사의 하도급계약에 대하여 「노무비 구분관리 및 지급확인제」 운영을 위하여 수급인과 하수급인은 다음 사항에 대하여 합의하고, 합의사항을 성실히 이행할 것을 확약합니다.</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-    </row>
-    <row r="14" ht="46.5" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    </row>
+    <row r="20" ht="4" customHeight="1"/>
+    <row r="21" ht="48.5" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>제1조(근거) 본 합의서는 계약예규 공사계약일반조건 제43조의 3(노무비의 구분관리 및 지급확인)의 규정에 근거한 ‘노무비 구분관리 및 지급확인제’(이하 ‘노무비 구분관리제’라 합니다.) 세부추진 사항을 합의하는데 그 목적이 있습니다.</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="46.5" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+    </row>
+    <row r="22" ht="48.5" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>제2조(정의) ‘노무비 구분관리제’란 발주자, 수급인 및 하수급인이 노무비를 노무비 이외의 대가와 구분하여, 발주자가 수급인에게 또는 수급인이 하수급인에게 노무비를 매월 지급하고 근로자에게 대금이 지급되었는지 여부를 확인하는 제도를 말합니다.</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
-    </row>
-    <row r="16" ht="46.5" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+    </row>
+    <row r="23" ht="48.5" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>제3조(대상공사 및 지급범위) 2012년 1월 1일 이후 발주자(                    )와 수급자가 도급계약 체결하는 공공공사(장기계속공사, ‘12년도 계속비 전환사업 포함)의 하도급계약을 체결한 공사현장에서 근무하는 모든 근로자(직접노무비 대상, 자재·장비 대금 제외)에게 지급합니다.</t>
         </is>
       </c>
-      <c r="G16" s="11" t="n"/>
-    </row>
-    <row r="17" ht="31" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>제4조(업무처리절차) 회계예규, 국토교통부 지침 및 발주처 세부계획에 따르며, 이 외 규정되어 있지 않은 사항은 국가계약법 등에 따라 양 당사자간의 합의에 따라 정합니다.</t>
         </is>
       </c>
-      <c r="G17" s="11" t="n"/>
-    </row>
-    <row r="18" ht="46.5" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+    </row>
+    <row r="25" ht="48.5" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>제5조(노무비 전용통장) 하수급인은 노무비 전용통장을 하수급인 명의로 개설함을 원칙으로 하나, 부득이한 사유가 발생할 시에는 수급자의 승인을 얻어 하수급인 이외명의로 통장을 개설할 수 있습니다. 전용통장의 변경도 수급자의 승인을 득하여야 합니다.</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+    </row>
+    <row r="26" ht="19.5" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>제6조(선급지급) 선급금에서 노무비는 제외되므로, 선급금 신청금액은 수급자와 협의하여 신청하도록 합니다.</t>
         </is>
       </c>
-      <c r="G19" s="11" t="n"/>
-    </row>
-    <row r="20" ht="31" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>제7조(지급상한) 노무비 청구액은 잔여 기성액을 초과하여 청구할 수 없으며, 하도급 계약액을 초과한 노무비에 대해서는 하도급사에서 지급하여야 합니다.</t>
         </is>
       </c>
-      <c r="G20" s="11" t="n"/>
-    </row>
-    <row r="21" ht="46.5" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>제8조(지급방법의 예외) 근로자가 계좌를 개설할 수 없거나 다른 방식으로 지급을 원하는 경우는 하수급자는 이에 이에 따라야 합니다. 하수급인의 경영상태 악화 등의 사유로 노임 구분관리제 실시가 어렵다고 판단될 경우 하수급인의 요청(동의)시에 수급자가 하수급인의 근로자에게 노무비를 직접 지급할 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="46.5" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+    </row>
+    <row r="28" ht="48.5" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>제8조(지급방법의 예외) 근로자가 계좌를 개설할 수 없거나 다른 방식으로 지급을 원하는 경우는 하수급자는 이에 따라야 합니다. 하수급인의 경영상태 악화 등의 사유로 노임 구분관리제 실시가 어렵다고 판단될 경우 하수급인의 요청(동의)시에 수급자가 하수급인의 근로자에게 노무비를 직접 지급할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48.5" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>제9조(성실의무) 하수급인은 노무비 청구내역의 누락 등이 발생하지 않도록 노무비 구분관리제를 성실하게 수행해야 합니다. 노무비 체불, 허위 청구 및 유용의 사례가 확인될 경우 발주자는 처분청 통보 및 형사고발 등의 행정조치를 할 수 있으며, 이에 대해 하수급자는 이의를 제기할 수 없습니다.</t>
         </is>
       </c>
-      <c r="G22" s="11" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>제10조 이 합의서에서 정하지 아니한 사항에 대하여는 수급자와 하수급자가 협의하여 정할 수 있습니다.</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="14" customHeight="1">
-      <c r="A24" s="15" t="n"/>
-      <c r="G24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="15" t="n"/>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>년          월          일</t>
-        </is>
-      </c>
-      <c r="G25" s="11" t="n"/>
-    </row>
-    <row r="26" ht="12" customHeight="1">
-      <c r="A26" s="15" t="n"/>
-      <c r="G26" s="11" t="n"/>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+    </row>
+    <row r="31" ht="8" customHeight="1"/>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="13" t="inlineStr"/>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년          월          일</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="4" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>계  약  자</t>
         </is>
       </c>
-      <c r="G27" s="11" t="n"/>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>수 급 자 :</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>성 명</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>성    명</t>
+        </is>
+      </c>
+      <c r="C35" s="13">
+        <f>IF(D6="","",D6)</f>
+        <v/>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>(인)</t>
         </is>
       </c>
-      <c r="G28" s="11" t="n"/>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="15" t="n"/>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>주 소</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="n"/>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="G35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="13" t="inlineStr"/>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>주    소</t>
+        </is>
+      </c>
+      <c r="C36" s="13">
+        <f>IF(D7="","",D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="13" t="inlineStr"/>
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>사업자번호</t>
         </is>
       </c>
-      <c r="G30" s="11" t="n"/>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="15" t="n"/>
-      <c r="G31" s="11" t="n"/>
-    </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="C37" s="18" t="n"/>
+      <c r="F37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38" ht="6" customHeight="1"/>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>하수급인 :</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>성 명</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>성    명</t>
+        </is>
+      </c>
+      <c r="C39" s="13">
+        <f>IF(D8="","",D8)</f>
+        <v/>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
         <is>
           <t>(인)</t>
         </is>
       </c>
-      <c r="G32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="15" t="n"/>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>주 소</t>
-        </is>
-      </c>
-      <c r="G33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="G39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="13" t="inlineStr"/>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>주    소</t>
+        </is>
+      </c>
+      <c r="C40" s="13">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="13" t="inlineStr"/>
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>사업자번호</t>
         </is>
       </c>
-      <c r="G34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="20" t="n"/>
-      <c r="B35" s="21" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="21" t="n"/>
-      <c r="F35" s="21" t="n"/>
-      <c r="G35" s="14" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="F41" s="13" t="inlineStr"/>
+    </row>
+    <row r="42" ht="6" customHeight="1"/>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>하늘색 칸 = 자동(하도급율 · 노무비 비율). 날인란의 성명·주소는 위 표의 «상호 및 대표자»·«영업소 소재지» 를 그대로 따라옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>제3조 괄호에는 그 현장 발주기관 이름을 적습니다. 발주기관이 정한 합의서 서식이 있으면 그 서식을 쓰세요.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="D3:G3"/>
+  <mergeCells count="55">
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="D9:G9"/>
+    <mergeCell ref="E13:G13"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="D12:G12"/>
+    <mergeCell ref="F16:G16"/>
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="D5:G5"/>
+    <mergeCell ref="E15:G15"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A5:C5"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="D10:G10"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="B13:C15"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="A8:A11"/>
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="C36:G36"/>
     <mergeCell ref="D11:G11"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D32:G32"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A3:G3"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A26:G26"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="23" min="0" max="16383" man="1"/>
-  </rowBreaks>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>【서식2】  하도급계약 체결시</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>「노무비 구분관리 및 지급확인제」 세부사항 합의서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="6" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>공  사  명</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>수급인</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>상호 및 대표자</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>예시건설(주) 대표이사 홍길동</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>영업소 소재지</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>가나시 마바로 45, 2층</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>하수급인</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>상호 및 대표자</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>(주)예시토건 대표이사 나대표</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>하도급 공종</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>철근·콘크리트공사(구조물공)</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>업종 및 등록번호</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>철근·콘크리트공사업 / 등록번호 000000</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>영업소 소재지
+(전화번호)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>가나시 가나로 12 (000-000-0000)</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>하도급
+내용</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>공  종</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>구조물공(암거) — 철근·거푸집·콘크리트</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>하도급내용</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>도 급 액</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>963241000</v>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>하도급액</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>285000000</v>
+      </c>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>하도급율</t>
+        </is>
+      </c>
+      <c r="E15" s="9">
+        <f>IF(OR(N(E13)=0,N(E14)=0),"",E14/E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>하도급계약상의
+직접노무비 또는
+노무비</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="8" t="n">
+        <v>85500000</v>
+      </c>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="10">
+        <f>IF(OR(N(D16)=0,N(E14)=0),"",D16/E14)</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="11">
+        <f>IF(AND(N(D16)&gt;0,N(E14)&gt;0,D16&gt;E14),"⚠ 노무비가 하도급액보다 큽니다 — 숫자를 확인하세요.",IF(AND(N(E14)&gt;0,N(E13)&gt;0,E14&gt;E13),"⚠ 하도급액이 도급액보다 큽니다 — 숫자를 확인하세요.",""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="2" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>위 시설공사의 하도급계약에 대하여 「노무비 구분관리 및 지급확인제」 운영을 위하여 수급인과 하수급인은 다음 사항에 대하여 합의하고, 합의사항을 성실히 이행할 것을 확약합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="4" customHeight="1"/>
+    <row r="21" ht="48.5" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>제1조(근거) 본 합의서는 계약예규 공사계약일반조건 제43조의 3(노무비의 구분관리 및 지급확인)의 규정에 근거한 ‘노무비 구분관리 및 지급확인제’(이하 ‘노무비 구분관리제’라 합니다.) 세부추진 사항을 합의하는데 그 목적이 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48.5" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>제2조(정의) ‘노무비 구분관리제’란 발주자, 수급인 및 하수급인이 노무비를 노무비 이외의 대가와 구분하여, 발주자가 수급인에게 또는 수급인이 하수급인에게 노무비를 매월 지급하고 근로자에게 대금이 지급되었는지 여부를 확인하는 제도를 말합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48.5" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>제3조(대상공사 및 지급범위) 2012년 1월 1일 이후 발주자(                    )와 수급자가 도급계약 체결하는 공공공사(장기계속공사, ‘12년도 계속비 전환사업 포함)의 하도급계약을 체결한 공사현장에서 근무하는 모든 근로자(직접노무비 대상, 자재·장비 대금 제외)에게 지급합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>제4조(업무처리절차) 회계예규, 국토교통부 지침 및 발주처 세부계획에 따르며, 이 외 규정되어 있지 않은 사항은 국가계약법 등에 따라 양 당사자간의 합의에 따라 정합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48.5" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>제5조(노무비 전용통장) 하수급인은 노무비 전용통장을 하수급인 명의로 개설함을 원칙으로 하나, 부득이한 사유가 발생할 시에는 수급자의 승인을 얻어 하수급인 이외명의로 통장을 개설할 수 있습니다. 전용통장의 변경도 수급자의 승인을 득하여야 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19.5" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>제6조(선급지급) 선급금에서 노무비는 제외되므로, 선급금 신청금액은 수급자와 협의하여 신청하도록 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>제7조(지급상한) 노무비 청구액은 잔여 기성액을 초과하여 청구할 수 없으며, 하도급 계약액을 초과한 노무비에 대해서는 하도급사에서 지급하여야 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48.5" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>제8조(지급방법의 예외) 근로자가 계좌를 개설할 수 없거나 다른 방식으로 지급을 원하는 경우는 하수급자는 이에 따라야 합니다. 하수급인의 경영상태 악화 등의 사유로 노임 구분관리제 실시가 어렵다고 판단될 경우 하수급인의 요청(동의)시에 수급자가 하수급인의 근로자에게 노무비를 직접 지급할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48.5" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>제9조(성실의무) 하수급인은 노무비 청구내역의 누락 등이 발생하지 않도록 노무비 구분관리제를 성실하게 수행해야 합니다. 노무비 체불, 허위 청구 및 유용의 사례가 확인될 경우 발주자는 처분청 통보 및 형사고발 등의 행정조치를 할 수 있으며, 이에 대해 하수급자는 이의를 제기할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>제10조 이 합의서에서 정하지 아니한 사항에 대하여는 수급자와 하수급자가 협의하여 정할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="8" customHeight="1"/>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="13" t="inlineStr"/>
+      <c r="D32" s="14" t="n">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="33" ht="4" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>계  약  자</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>수 급 자 :</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>성    명</t>
+        </is>
+      </c>
+      <c r="C35" s="13">
+        <f>IF(D6="","",D6)</f>
+        <v/>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>(인)</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="13" t="inlineStr"/>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>주    소</t>
+        </is>
+      </c>
+      <c r="C36" s="13">
+        <f>IF(D7="","",D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="13" t="inlineStr"/>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>사업자번호</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38" ht="6" customHeight="1"/>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>하수급인 :</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>성    명</t>
+        </is>
+      </c>
+      <c r="C39" s="13">
+        <f>IF(D8="","",D8)</f>
+        <v/>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>(인)</t>
+        </is>
+      </c>
+      <c r="G39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="13" t="inlineStr"/>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>주    소</t>
+        </is>
+      </c>
+      <c r="C40" s="13">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="13" t="inlineStr"/>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>사업자번호</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>000-00-00000</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr"/>
+    </row>
+    <row r="42" ht="6" customHeight="1"/>
+    <row r="44" ht="19.5" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="54">
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="B13:C15"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A23:G23"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/nomubi-gubun-haeui.xlsx
+++ b/web/public/forms/nomubi-gubun-haeui.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="20" t="inlineStr">

--- a/web/public/forms/nomubi-gubun-haeui.xlsx
+++ b/web/public/forms/nomubi-gubun-haeui.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="합의서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'합의서'!$A$1:$G$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$G$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -135,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -191,9 +189,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -756,10 +751,7 @@
           <t>하도급율</t>
         </is>
       </c>
-      <c r="E15" s="9">
-        <f>IF(OR(N(E13)=0,N(E14)=0),"",E14/E13)</f>
-        <v/>
-      </c>
+      <c r="E15" s="9" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
     </row>
@@ -775,17 +767,11 @@
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="10">
-        <f>IF(OR(N(D16)=0,N(E14)=0),"",D16/E14)</f>
-        <v/>
-      </c>
+      <c r="F16" s="10" t="n"/>
       <c r="G16" s="6" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="11">
-        <f>IF(AND(N(D16)&gt;0,N(E14)&gt;0,D16&gt;E14),"⚠ 노무비가 하도급액보다 큽니다 — 숫자를 확인하세요.",IF(AND(N(E14)&gt;0,N(E13)&gt;0,E14&gt;E13),"⚠ 하도급액이 도급액보다 큽니다 — 숫자를 확인하세요.",""))</f>
-        <v/>
-      </c>
+      <c r="A17" s="11" t="n"/>
     </row>
     <row r="18" ht="2" customHeight="1"/>
     <row r="19" ht="34" customHeight="1">
@@ -894,10 +880,7 @@
           <t>성    명</t>
         </is>
       </c>
-      <c r="C35" s="13">
-        <f>IF(D6="","",D6)</f>
-        <v/>
-      </c>
+      <c r="C35" s="13" t="n"/>
       <c r="F35" s="17" t="inlineStr">
         <is>
           <t>(인)</t>
@@ -912,10 +895,7 @@
           <t>주    소</t>
         </is>
       </c>
-      <c r="C36" s="13">
-        <f>IF(D7="","",D7)</f>
-        <v/>
-      </c>
+      <c r="C36" s="13" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="13" t="inlineStr"/>
@@ -939,10 +919,7 @@
           <t>성    명</t>
         </is>
       </c>
-      <c r="C39" s="13">
-        <f>IF(D8="","",D8)</f>
-        <v/>
-      </c>
+      <c r="C39" s="13" t="n"/>
       <c r="F39" s="17" t="inlineStr">
         <is>
           <t>(인)</t>
@@ -957,10 +934,7 @@
           <t>주    소</t>
         </is>
       </c>
-      <c r="C40" s="13">
-        <f>IF(D11="","",D11)</f>
-        <v/>
-      </c>
+      <c r="C40" s="13" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="13" t="inlineStr"/>
@@ -973,6 +947,7 @@
       <c r="F41" s="13" t="inlineStr"/>
     </row>
     <row r="42" ht="6" customHeight="1"/>
+    <row r="43"/>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="19" t="inlineStr">
         <is>
@@ -1049,538 +1024,4 @@
   <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="E1" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>【서식2】  하도급계약 체결시</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>「노무비 구분관리 및 지급확인제」 세부사항 합의서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="6" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>공  사  명</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>수급인</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>상호 및 대표자</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>예시건설(주) 대표이사 홍길동</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>영업소 소재지</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>가나시 마바로 45, 2층</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>하수급인</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>상호 및 대표자</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>(주)예시토건 대표이사 나대표</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>하도급 공종</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>철근·콘크리트공사(구조물공)</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>업종 및 등록번호</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>철근·콘크리트공사업 / 등록번호 000000</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>영업소 소재지
-(전화번호)</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>가나시 가나로 12 (000-000-0000)</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>하도급
-내용</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>공  종</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>구조물공(암거) — 철근·거푸집·콘크리트</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>하도급내용</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>도 급 액</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>963241000</v>
-      </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>하도급액</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>285000000</v>
-      </c>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>하도급율</t>
-        </is>
-      </c>
-      <c r="E15" s="9">
-        <f>IF(OR(N(E13)=0,N(E14)=0),"",E14/E13)</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>하도급계약상의
-직접노무비 또는
-노무비</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="8" t="n">
-        <v>85500000</v>
-      </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="10">
-        <f>IF(OR(N(D16)=0,N(E14)=0),"",D16/E14)</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="11">
-        <f>IF(AND(N(D16)&gt;0,N(E14)&gt;0,D16&gt;E14),"⚠ 노무비가 하도급액보다 큽니다 — 숫자를 확인하세요.",IF(AND(N(E14)&gt;0,N(E13)&gt;0,E14&gt;E13),"⚠ 하도급액이 도급액보다 큽니다 — 숫자를 확인하세요.",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="2" customHeight="1"/>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>위 시설공사의 하도급계약에 대하여 「노무비 구분관리 및 지급확인제」 운영을 위하여 수급인과 하수급인은 다음 사항에 대하여 합의하고, 합의사항을 성실히 이행할 것을 확약합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="4" customHeight="1"/>
-    <row r="21" ht="48.5" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>제1조(근거) 본 합의서는 계약예규 공사계약일반조건 제43조의 3(노무비의 구분관리 및 지급확인)의 규정에 근거한 ‘노무비 구분관리 및 지급확인제’(이하 ‘노무비 구분관리제’라 합니다.) 세부추진 사항을 합의하는데 그 목적이 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48.5" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>제2조(정의) ‘노무비 구분관리제’란 발주자, 수급인 및 하수급인이 노무비를 노무비 이외의 대가와 구분하여, 발주자가 수급인에게 또는 수급인이 하수급인에게 노무비를 매월 지급하고 근로자에게 대금이 지급되었는지 여부를 확인하는 제도를 말합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="48.5" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>제3조(대상공사 및 지급범위) 2012년 1월 1일 이후 발주자(                    )와 수급자가 도급계약 체결하는 공공공사(장기계속공사, ‘12년도 계속비 전환사업 포함)의 하도급계약을 체결한 공사현장에서 근무하는 모든 근로자(직접노무비 대상, 자재·장비 대금 제외)에게 지급합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>제4조(업무처리절차) 회계예규, 국토교통부 지침 및 발주처 세부계획에 따르며, 이 외 규정되어 있지 않은 사항은 국가계약법 등에 따라 양 당사자간의 합의에 따라 정합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48.5" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>제5조(노무비 전용통장) 하수급인은 노무비 전용통장을 하수급인 명의로 개설함을 원칙으로 하나, 부득이한 사유가 발생할 시에는 수급자의 승인을 얻어 하수급인 이외명의로 통장을 개설할 수 있습니다. 전용통장의 변경도 수급자의 승인을 득하여야 합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>제6조(선급지급) 선급금에서 노무비는 제외되므로, 선급금 신청금액은 수급자와 협의하여 신청하도록 합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>제7조(지급상한) 노무비 청구액은 잔여 기성액을 초과하여 청구할 수 없으며, 하도급 계약액을 초과한 노무비에 대해서는 하도급사에서 지급하여야 합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48.5" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>제8조(지급방법의 예외) 근로자가 계좌를 개설할 수 없거나 다른 방식으로 지급을 원하는 경우는 하수급자는 이에 따라야 합니다. 하수급인의 경영상태 악화 등의 사유로 노임 구분관리제 실시가 어렵다고 판단될 경우 하수급인의 요청(동의)시에 수급자가 하수급인의 근로자에게 노무비를 직접 지급할 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="48.5" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>제9조(성실의무) 하수급인은 노무비 청구내역의 누락 등이 발생하지 않도록 노무비 구분관리제를 성실하게 수행해야 합니다. 노무비 체불, 허위 청구 및 유용의 사례가 확인될 경우 발주자는 처분청 통보 및 형사고발 등의 행정조치를 할 수 있으며, 이에 대해 하수급자는 이의를 제기할 수 없습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>제10조 이 합의서에서 정하지 아니한 사항에 대하여는 수급자와 하수급자가 협의하여 정할 수 있습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="8" customHeight="1"/>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="13" t="inlineStr"/>
-      <c r="D32" s="14" t="n">
-        <v>46143</v>
-      </c>
-    </row>
-    <row r="33" ht="4" customHeight="1"/>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>계  약  자</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>수 급 자 :</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>성    명</t>
-        </is>
-      </c>
-      <c r="C35" s="13">
-        <f>IF(D6="","",D6)</f>
-        <v/>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-      <c r="G35" s="13" t="inlineStr"/>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="13" t="inlineStr"/>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>주    소</t>
-        </is>
-      </c>
-      <c r="C36" s="13">
-        <f>IF(D7="","",D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="13" t="inlineStr"/>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>사업자번호</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="inlineStr"/>
-    </row>
-    <row r="38" ht="6" customHeight="1"/>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>하수급인 :</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>성    명</t>
-        </is>
-      </c>
-      <c r="C39" s="13">
-        <f>IF(D8="","",D8)</f>
-        <v/>
-      </c>
-      <c r="F39" s="17" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-      <c r="G39" s="13" t="inlineStr"/>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="13" t="inlineStr"/>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>주    소</t>
-        </is>
-      </c>
-      <c r="C40" s="13">
-        <f>IF(D11="","",D11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="13" t="inlineStr"/>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>사업자번호</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>000-00-00000</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="inlineStr"/>
-    </row>
-    <row r="42" ht="6" customHeight="1"/>
-    <row r="44" ht="19.5" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 회사 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="B13:C15"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A23:G23"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/nomubi-gubun-haeui.xlsx
+++ b/web/public/forms/nomubi-gubun-haeui.xlsx
@@ -570,7 +570,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
